--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job History" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -525,17 +525,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>f6e573ccef82cc55</t>
+          <t>bad3b7db83f498d3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -545,32 +545,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/</t>
+          <t>https://dxc.com/us/en/careers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Java Full Stack Remote United Kingdom United Kingdom of Great Britain and Northern Ireland</t>
+          <t>Java Software Engineer with Japanese</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26676</t>
+          <t>https://careers.dxc.com/job/23900875/java-software-engineer-with-japanese-tan-binh-vn/</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>software engineer java</t>
+          <t>software engineer</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -578,31 +578,29 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="L2" t="n">
+        <v>65</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>e3814f0fe9843500</t>
+          <t>f6e573ccef82cc55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -627,12 +625,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Java Full Stack Remote United States United States of America</t>
+          <t>Full Stack Software Engineer Java Full Stack Remote United Kingdom United Kingdom of Great Britain and Northern Ireland</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26677</t>
+          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26676</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -679,12 +677,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>eef17e6ffbd5fcc3</t>
+          <t>e3814f0fe9843500</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -704,12 +702,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Regular Software Engineer Java Krakow Poland</t>
+          <t>Full Stack Software Engineer Java Full Stack Remote United States United States of America</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
+          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26677</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -744,29 +742,29 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>958584b0e00fb2a6</t>
+          <t>eef17e6ffbd5fcc3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -776,22 +774,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://career.luxoft.com/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Regular Software Engineer Java Krakow Poland</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
+          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -801,17 +799,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer java</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -821,19 +819,19 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>e0c2e763389249fb</t>
+          <t>958584b0e00fb2a6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -863,7 +861,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -910,7 +908,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>f59eedfdb81604eb</t>
+          <t>e0c2e763389249fb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -940,7 +938,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -987,7 +985,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6639b28e3e83df1b</t>
+          <t>f59eedfdb81604eb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1017,7 +1015,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1064,7 +1062,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>db41fec42eff7fc7</t>
+          <t>6639b28e3e83df1b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1094,7 +1092,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1141,7 +1139,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7e7876fb53aec018</t>
+          <t>db41fec42eff7fc7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1171,7 +1169,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1218,7 +1216,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>c7d16ed243960564</t>
+          <t>7e7876fb53aec018</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1248,7 +1246,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1295,7 +1293,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06c47b6859dcf9d9</t>
+          <t>c7d16ed243960564</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1325,7 +1323,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1372,7 +1370,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3add5db664f895b3</t>
+          <t>06c47b6859dcf9d9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1402,7 +1400,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1449,7 +1447,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>75512c01a06f9149</t>
+          <t>3add5db664f895b3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1479,7 +1477,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1526,7 +1524,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>e6f90d90e6d9ac49</t>
+          <t>75512c01a06f9149</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1556,7 +1554,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1603,7 +1601,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bcf6618b2c949330</t>
+          <t>e6f90d90e6d9ac49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1633,7 +1631,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1680,7 +1678,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00340054a5ab077b</t>
+          <t>bcf6618b2c949330</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1710,7 +1708,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1757,7 +1755,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>521187917c773da4</t>
+          <t>00340054a5ab077b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1787,7 +1785,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1834,7 +1832,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>39d7af8a3712173d</t>
+          <t>521187917c773da4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1864,7 +1862,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1911,7 +1909,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>b35b4abb2ec1b6cf</t>
+          <t>39d7af8a3712173d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1941,7 +1939,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1988,7 +1986,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cc643671602a4ad6</t>
+          <t>b35b4abb2ec1b6cf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2018,7 +2016,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2065,7 +2063,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>e89acee1e60e4e15</t>
+          <t>cc643671602a4ad6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2095,7 +2093,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
+          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2142,7 +2140,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>e2c7cfa23e04ecc5</t>
+          <t>e89acee1e60e4e15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2172,7 +2170,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
+          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2219,7 +2217,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>f264b25e9b13643e</t>
+          <t>e2c7cfa23e04ecc5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2249,7 +2247,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
+          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2296,7 +2294,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2718ac706b7b8fca</t>
+          <t>f264b25e9b13643e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2321,12 +2319,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shortlisted</t>
+          <t>Read more</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/#/</t>
+          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2373,82 +2371,1655 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>d4301ec4cb541a49</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-angular-and-cloud-services-publics-bordeaux-in-merignac-france-jid-216</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>57</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>5a9a92ff42d402b5</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-full-stack-monetique-typescript-go-services-financiers-paris-kanest-xgen-in-courbevoie-france-jid-9847</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>57</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>f10b2d50a2eab2ed</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-de-solutions-de-test-monetique-services-financiers-paris-kanest-in-courbevoie-france-jid-9846</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>57</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>d37352caded60682</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/reconversion-consultant-e-sap-toulouse-in-colomiers-france-jid-9845</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>57</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ac20d4a800fe2783</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/devops-test-engineer-in-nieuwegein-netherlands-jid-4314</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>57</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dfa7136b5b89a9fe</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/qa-consultant-in-nieuwegein-netherlands-jid-5365</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>57</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8c80575a53c5eeaa</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/developpeur-se-python-devops-services-financiers-paris-in-paris-france-jid-8938</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>57</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>c50aedde915c89b5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-orleans-in-orleans-france-jid-7170</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>57</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>06c5acd32fb73502</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-react-angular-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7171</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>57</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7947819c85cba4b7</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/developpeur-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4782</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>57</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ee86d75ecad18f62</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/developpeur-expert-java-services-financiers-ile-de-france-in-paris-france-jid-4806</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>57</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>138c41eaeddd3365</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/ingenieur-e-systemes-calculateurs-embarques-industrie-le-plessis-robinson-in-le-plessis-robinson-france-jid-9463</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>57</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>83618a239b34fb89</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7169</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>57</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6edaac1727441aa5</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/tech-lead-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4790</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>57</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>6c16f2ba70ae52ae</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/junior-support-engineer-24-7-in-brussels-belgium-jid-1614</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>57</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>50bdd6d8ed2ce309</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/test-automation-consultant-in-nieuwegein-netherlands-jid-4313</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>57</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>27c9ec0a346e8d8a</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/chef-de-projet-it-adjoint-defense-and-securite-rennes-in-cesson-sevigne-france-jid-3750</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>57</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>12e5e7e963276a4f</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/bps-non-voice-team-member-six-month-contractual-job-in-chennai-tamil-nadu-india-jid-9844</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>57</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>9d6a28477b4aeb27</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/cybersecurity-team-lead-consultant-in-singapore-jid-9296</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>57</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>9f665ce19a03b2ab</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/manager-anti-financial-crime-operations-ai-and-managed-services-m-w-d-in-bundesweit-germany-jid-9843</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>57</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2718ac706b7b8fca</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/#/</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>57</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Still Open</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>71596b406dea22d9</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sopra Steria</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Service-Based</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://www.soprasteria.com/careers</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>View all</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>https://careers.soprasteria.com/jobs</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>java, git</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>java/backend keyword</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>associate</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Not Seen Today</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>57</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Still Open</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O26"/>
+  <autoFilter ref="A1:O47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Still Open</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2424,8 +2424,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>57</v>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -2499,8 +2501,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L27" t="n">
-        <v>57</v>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -2574,8 +2578,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L28" t="n">
-        <v>57</v>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2649,8 +2655,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>57</v>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2724,8 +2732,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>57</v>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2799,8 +2809,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>57</v>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2874,8 +2886,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>57</v>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2949,8 +2963,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>57</v>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -3024,8 +3040,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>57</v>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -3099,8 +3117,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>57</v>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -3174,8 +3194,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L36" t="n">
-        <v>57</v>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3249,8 +3271,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>57</v>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -3324,8 +3348,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L38" t="n">
-        <v>57</v>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3399,8 +3425,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L39" t="n">
-        <v>57</v>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -3474,8 +3502,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L40" t="n">
-        <v>57</v>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3549,8 +3579,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L41" t="n">
-        <v>57</v>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -3624,8 +3656,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L42" t="n">
-        <v>57</v>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -3699,8 +3733,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L43" t="n">
-        <v>57</v>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -3774,8 +3810,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L44" t="n">
-        <v>57</v>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -3849,8 +3887,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L45" t="n">
-        <v>57</v>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -3924,8 +3964,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L46" t="n">
-        <v>57</v>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -3999,8 +4041,10 @@
           <t>entry level</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>57</v>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>

--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -578,12 +578,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>65</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Still Open</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2431,7 +2433,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2508,7 +2510,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2585,7 +2587,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2662,7 +2664,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2739,7 +2741,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2816,7 +2818,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2893,7 +2895,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2970,7 +2972,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3047,7 +3049,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3124,7 +3126,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3201,7 +3203,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3278,7 +3280,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3355,7 +3357,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3432,7 +3434,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3509,7 +3511,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3586,7 +3588,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3663,7 +3665,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3740,7 +3742,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3817,7 +3819,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3894,7 +3896,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3971,7 +3973,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Still Open</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4048,7 +4050,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Still Open</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">

--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job History" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -525,17 +525,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bad3b7db83f498d3</t>
+          <t>f156221e2062d0eb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Cognizant BPS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -545,74 +545,72 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://dxc.com/us/en/careers</t>
+          <t>https://careers.cognizant.com/india-en/</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Java Software Engineer with Japanese</t>
+          <t>Java Developer(AWS)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://careers.dxc.com/job/23900875/java-software-engineer-with-japanese-tan-binh-vn/</t>
+          <t>https://careers.cognizant.com/india-en/jobs/00070527821/java-developer-aws/</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>India, Chennai</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>java developer</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>java</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>software engineer</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="L2" t="n">
+        <v>100</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f6e573ccef82cc55</t>
+          <t>50232bd6461a629f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Cognizant Digital Experience</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -622,32 +620,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/</t>
+          <t>https://careers.cognizant.com/india-en/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Java Full Stack Remote United Kingdom United Kingdom of Great Britain and Northern Ireland</t>
+          <t>Java Developer(AWS)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26676</t>
+          <t>https://careers.cognizant.com/india-en/jobs/00070527821/java-developer-aws/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India, Chennai</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>software engineer java</t>
+          <t>java developer</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -655,41 +653,39 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="L3" t="n">
+        <v>100</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>e3814f0fe9843500</t>
+          <t>41b78c6d2ab9f3f6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Cognizant Softvision</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -699,32 +695,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/</t>
+          <t>https://careers.cognizant.com/india-en/</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Java Full Stack Remote United States United States of America</t>
+          <t>Java Developer(AWS)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26677</t>
+          <t>https://careers.cognizant.com/india-en/jobs/00070527821/java-developer-aws/</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India, Chennai</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>software engineer java</t>
+          <t>java developer</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -732,41 +728,39 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="L4" t="n">
+        <v>100</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>eef17e6ffbd5fcc3</t>
+          <t>c2e2f6631106e75f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Cognizant Testing Services</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -776,32 +770,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/</t>
+          <t>https://careers.cognizant.com/india-en/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Regular Software Engineer Java Krakow Poland</t>
+          <t>Java Developer(AWS)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
+          <t>https://careers.cognizant.com/india-en/jobs/00070527821/java-developer-aws/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India, Chennai</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>software engineer java</t>
+          <t>java developer</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -809,41 +803,39 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="L5" t="n">
+        <v>100</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>958584b0e00fb2a6</t>
+          <t>bad3b7db83f498d3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -853,42 +845,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://dxc.com/us/en/careers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Java Software Engineer with Japanese</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
+          <t>https://careers.dxc.com/job/23900875/java-software-engineer-with-japanese-tan-binh-vn/</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -898,29 +890,29 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>e0c2e763389249fb</t>
+          <t>f6e573ccef82cc55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -930,22 +922,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://career.luxoft.com/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Full Stack Software Engineer Java Full Stack Remote United Kingdom United Kingdom of Great Britain and Northern Ireland</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
+          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26676</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -955,17 +947,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer java</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -975,29 +967,29 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>f59eedfdb81604eb</t>
+          <t>e3814f0fe9843500</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1007,22 +999,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://career.luxoft.com/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Full Stack Software Engineer Java Full Stack Remote United States United States of America</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
+          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26677</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1032,17 +1024,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer java</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1052,29 +1044,29 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6639b28e3e83df1b</t>
+          <t>eef17e6ffbd5fcc3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1084,22 +1076,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://career.luxoft.com/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Regular Software Engineer Java Krakow Poland</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
+          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1109,17 +1101,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer java</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1129,19 +1121,19 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>db41fec42eff7fc7</t>
+          <t>958584b0e00fb2a6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1171,7 +1163,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1218,7 +1210,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7e7876fb53aec018</t>
+          <t>e0c2e763389249fb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1248,7 +1240,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1295,7 +1287,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>c7d16ed243960564</t>
+          <t>f59eedfdb81604eb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1325,7 +1317,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1372,7 +1364,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06c47b6859dcf9d9</t>
+          <t>6639b28e3e83df1b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1402,7 +1394,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1449,7 +1441,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3add5db664f895b3</t>
+          <t>db41fec42eff7fc7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1479,7 +1471,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1526,7 +1518,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>75512c01a06f9149</t>
+          <t>7e7876fb53aec018</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1556,7 +1548,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1603,7 +1595,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>e6f90d90e6d9ac49</t>
+          <t>c7d16ed243960564</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1633,7 +1625,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1680,7 +1672,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bcf6618b2c949330</t>
+          <t>06c47b6859dcf9d9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1710,7 +1702,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1757,7 +1749,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00340054a5ab077b</t>
+          <t>3add5db664f895b3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1787,7 +1779,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1834,7 +1826,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>521187917c773da4</t>
+          <t>75512c01a06f9149</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1864,7 +1856,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1911,7 +1903,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>39d7af8a3712173d</t>
+          <t>e6f90d90e6d9ac49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1941,7 +1933,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1988,7 +1980,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>b35b4abb2ec1b6cf</t>
+          <t>bcf6618b2c949330</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2018,7 +2010,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2065,7 +2057,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cc643671602a4ad6</t>
+          <t>00340054a5ab077b</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2095,7 +2087,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2142,7 +2134,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>e89acee1e60e4e15</t>
+          <t>521187917c773da4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2172,7 +2164,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2219,7 +2211,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>e2c7cfa23e04ecc5</t>
+          <t>39d7af8a3712173d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2249,7 +2241,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2296,7 +2288,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>f264b25e9b13643e</t>
+          <t>b35b4abb2ec1b6cf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2326,7 +2318,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2373,12 +2365,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>d4301ec4cb541a49</t>
+          <t>cc643671602a4ad6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2403,7 +2395,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-java-angular-and-cloud-services-publics-bordeaux-in-merignac-france-jid-216</t>
+          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2413,7 +2405,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2423,12 +2415,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2438,24 +2430,24 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5a9a92ff42d402b5</t>
+          <t>e89acee1e60e4e15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2480,7 +2472,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-full-stack-monetique-typescript-go-services-financiers-paris-kanest-xgen-in-courbevoie-france-jid-9847</t>
+          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2490,7 +2482,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2500,12 +2492,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2515,24 +2507,24 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>f10b2d50a2eab2ed</t>
+          <t>e2c7cfa23e04ecc5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2557,7 +2549,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-de-solutions-de-test-monetique-services-financiers-paris-kanest-in-courbevoie-france-jid-9846</t>
+          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2567,7 +2559,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2577,12 +2569,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2592,24 +2584,24 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>d37352caded60682</t>
+          <t>f264b25e9b13643e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2634,7 +2626,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/reconversion-consultant-e-sap-toulouse-in-colomiers-france-jid-9845</t>
+          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2644,7 +2636,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2654,12 +2646,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2669,19 +2661,19 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ac20d4a800fe2783</t>
+          <t>d4301ec4cb541a49</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2711,7 +2703,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/devops-test-engineer-in-nieuwegein-netherlands-jid-4314</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-angular-and-cloud-services-publics-bordeaux-in-merignac-france-jid-216</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2758,7 +2750,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>dfa7136b5b89a9fe</t>
+          <t>5a9a92ff42d402b5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2788,7 +2780,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/qa-consultant-in-nieuwegein-netherlands-jid-5365</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-full-stack-monetique-typescript-go-services-financiers-paris-kanest-xgen-in-courbevoie-france-jid-9847</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2835,7 +2827,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8c80575a53c5eeaa</t>
+          <t>f10b2d50a2eab2ed</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2865,7 +2857,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-python-devops-services-financiers-paris-in-paris-france-jid-8938</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-de-solutions-de-test-monetique-services-financiers-paris-kanest-in-courbevoie-france-jid-9846</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2912,7 +2904,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>c50aedde915c89b5</t>
+          <t>d37352caded60682</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2942,7 +2934,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-orleans-in-orleans-france-jid-7170</t>
+          <t>https://careers.soprasteria.com/job/reconversion-consultant-e-sap-toulouse-in-colomiers-france-jid-9845</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2989,7 +2981,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06c5acd32fb73502</t>
+          <t>ac20d4a800fe2783</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3019,7 +3011,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-react-angular-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7171</t>
+          <t>https://careers.soprasteria.com/job/devops-test-engineer-in-nieuwegein-netherlands-jid-4314</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3066,7 +3058,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7947819c85cba4b7</t>
+          <t>dfa7136b5b89a9fe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3096,7 +3088,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4782</t>
+          <t>https://careers.soprasteria.com/job/qa-consultant-in-nieuwegein-netherlands-jid-5365</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3143,7 +3135,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ee86d75ecad18f62</t>
+          <t>8c80575a53c5eeaa</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3173,7 +3165,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-expert-java-services-financiers-ile-de-france-in-paris-france-jid-4806</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-python-devops-services-financiers-paris-in-paris-france-jid-8938</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3220,7 +3212,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>138c41eaeddd3365</t>
+          <t>c50aedde915c89b5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3250,7 +3242,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/ingenieur-e-systemes-calculateurs-embarques-industrie-le-plessis-robinson-in-le-plessis-robinson-france-jid-9463</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-orleans-in-orleans-france-jid-7170</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3297,7 +3289,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>83618a239b34fb89</t>
+          <t>06c5acd32fb73502</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3327,7 +3319,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-java-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7169</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-react-angular-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7171</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3374,7 +3366,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6edaac1727441aa5</t>
+          <t>7947819c85cba4b7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3404,7 +3396,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4790</t>
+          <t>https://careers.soprasteria.com/job/developpeur-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4782</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3451,7 +3443,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6c16f2ba70ae52ae</t>
+          <t>ee86d75ecad18f62</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3481,7 +3473,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/junior-support-engineer-24-7-in-brussels-belgium-jid-1614</t>
+          <t>https://careers.soprasteria.com/job/developpeur-expert-java-services-financiers-ile-de-france-in-paris-france-jid-4806</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3528,7 +3520,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>50bdd6d8ed2ce309</t>
+          <t>138c41eaeddd3365</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3558,7 +3550,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/test-automation-consultant-in-nieuwegein-netherlands-jid-4313</t>
+          <t>https://careers.soprasteria.com/job/ingenieur-e-systemes-calculateurs-embarques-industrie-le-plessis-robinson-in-le-plessis-robinson-france-jid-9463</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3605,7 +3597,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>27c9ec0a346e8d8a</t>
+          <t>83618a239b34fb89</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3635,7 +3627,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/chef-de-projet-it-adjoint-defense-and-securite-rennes-in-cesson-sevigne-france-jid-3750</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7169</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3682,7 +3674,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12e5e7e963276a4f</t>
+          <t>6edaac1727441aa5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3712,7 +3704,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/bps-non-voice-team-member-six-month-contractual-job-in-chennai-tamil-nadu-india-jid-9844</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4790</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3759,7 +3751,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9d6a28477b4aeb27</t>
+          <t>6c16f2ba70ae52ae</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3789,7 +3781,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/cybersecurity-team-lead-consultant-in-singapore-jid-9296</t>
+          <t>https://careers.soprasteria.com/job/junior-support-engineer-24-7-in-brussels-belgium-jid-1614</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3836,7 +3828,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9f665ce19a03b2ab</t>
+          <t>50bdd6d8ed2ce309</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3866,7 +3858,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/manager-anti-financial-crime-operations-ai-and-managed-services-m-w-d-in-bundesweit-germany-jid-9843</t>
+          <t>https://careers.soprasteria.com/job/test-automation-consultant-in-nieuwegein-netherlands-jid-4313</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3913,7 +3905,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2718ac706b7b8fca</t>
+          <t>27c9ec0a346e8d8a</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3938,12 +3930,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shortlisted</t>
+          <t>Read more</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/#/</t>
+          <t>https://careers.soprasteria.com/job/chef-de-projet-it-adjoint-defense-and-securite-rennes-in-cesson-sevigne-france-jid-3750</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3978,7 +3970,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3990,82 +3982,390 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>12e5e7e963276a4f</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/bps-non-voice-team-member-six-month-contractual-job-in-chennai-tamil-nadu-india-jid-9844</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>9d6a28477b4aeb27</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/cybersecurity-team-lead-consultant-in-singapore-jid-9296</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>9f665ce19a03b2ab</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/manager-anti-financial-crime-operations-ai-and-managed-services-m-w-d-in-bundesweit-germany-jid-9843</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2718ac706b7b8fca</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/#/</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>71596b406dea22d9</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>Sopra Steria</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Service-Based</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>https://www.soprasteria.com/careers</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>View all</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>https://careers.soprasteria.com/jobs</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>java</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>java/backend keyword</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>entry level</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Not Seen Today</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O47"/>
+  <autoFilter ref="A1:O51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -578,12 +578,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>100</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -653,12 +655,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>100</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,12 +732,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>100</v>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -803,12 +809,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>100</v>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">

--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job History" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -602,17 +602,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>50232bd6461a629f</t>
+          <t>e0e5d4bee485ddff</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cognizant Digital Experience</t>
+          <t>Cognizant BPS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -627,17 +627,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Java Developer(AWS)</t>
+          <t>Java Developer(React)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://careers.cognizant.com/india-en/jobs/00070527821/java-developer-aws/</t>
+          <t>https://careers.cognizant.com/india-en/jobs/00070529151/java-developer-react/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>India, Chennai</t>
+          <t>India, Pune</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -655,31 +655,29 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="L3" t="n">
+        <v>100</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>41b78c6d2ab9f3f6</t>
+          <t>50232bd6461a629f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -689,7 +687,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cognizant Softvision</t>
+          <t>Cognizant Digital Experience</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -756,17 +754,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>c2e2f6631106e75f</t>
+          <t>d0ae1efd23ce3edf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cognizant Testing Services</t>
+          <t>Cognizant Digital Experience</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -781,17 +779,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Java Developer(AWS)</t>
+          <t>Java Developer(React)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://careers.cognizant.com/india-en/jobs/00070527821/java-developer-aws/</t>
+          <t>https://careers.cognizant.com/india-en/jobs/00070529151/java-developer-react/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>India, Chennai</t>
+          <t>India, Pune</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -809,41 +807,39 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="L5" t="n">
+        <v>100</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bad3b7db83f498d3</t>
+          <t>41b78c6d2ab9f3f6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DXC Technology</t>
+          <t>Cognizant Softvision</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -853,42 +849,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://dxc.com/us/en/careers</t>
+          <t>https://careers.cognizant.com/india-en/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Java Software Engineer with Japanese</t>
+          <t>Java Developer(AWS)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://careers.dxc.com/job/23900875/java-software-engineer-with-japanese-tan-binh-vn/</t>
+          <t>https://careers.cognizant.com/india-en/jobs/00070527821/java-developer-aws/</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>India, Chennai</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>java developer</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>java</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>software engineer</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -898,29 +894,29 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>f6e573ccef82cc55</t>
+          <t>96ab92555e9abec2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Cognizant Softvision</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -930,32 +926,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/</t>
+          <t>https://careers.cognizant.com/india-en/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Java Full Stack Remote United Kingdom United Kingdom of Great Britain and Northern Ireland</t>
+          <t>Java Developer(React)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26676</t>
+          <t>https://careers.cognizant.com/india-en/jobs/00070529151/java-developer-react/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India, Pune</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>software engineer java</t>
+          <t>java developer</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -963,41 +959,39 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="L7" t="n">
+        <v>100</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>e3814f0fe9843500</t>
+          <t>c2e2f6631106e75f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Cognizant Testing Services</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1007,32 +1001,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/</t>
+          <t>https://careers.cognizant.com/india-en/</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Java Full Stack Remote United States United States of America</t>
+          <t>Java Developer(AWS)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26677</t>
+          <t>https://careers.cognizant.com/india-en/jobs/00070527821/java-developer-aws/</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India, Chennai</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>software engineer java</t>
+          <t>java developer</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1042,7 +1036,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1052,29 +1046,29 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>eef17e6ffbd5fcc3</t>
+          <t>81bcac45b5d4fb48</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Cognizant Testing Services</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1084,32 +1078,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/</t>
+          <t>https://careers.cognizant.com/india-en/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Regular Software Engineer Java Krakow Poland</t>
+          <t>Java Developer(React)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
+          <t>https://careers.cognizant.com/india-en/jobs/00070529151/java-developer-react/</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India, Pune</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>software engineer java</t>
+          <t>java developer</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1117,41 +1111,39 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="L9" t="n">
+        <v>100</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>958584b0e00fb2a6</t>
+          <t>bad3b7db83f498d3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1161,42 +1153,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://dxc.com/us/en/careers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Java Software Engineer with Japanese</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
+          <t>https://careers.dxc.com/job/23900875/java-software-engineer-with-japanese-tan-binh-vn/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1206,29 +1198,29 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>e0c2e763389249fb</t>
+          <t>f6e573ccef82cc55</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1238,22 +1230,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://career.luxoft.com/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Full Stack Software Engineer Java Full Stack Remote United Kingdom United Kingdom of Great Britain and Northern Ireland</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
+          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26676</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1263,17 +1255,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer java</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1283,29 +1275,29 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f59eedfdb81604eb</t>
+          <t>e3814f0fe9843500</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1315,22 +1307,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://career.luxoft.com/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Full Stack Software Engineer Java Full Stack Remote United States United States of America</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
+          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26677</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1340,17 +1332,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer java</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1360,29 +1352,29 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6639b28e3e83df1b</t>
+          <t>eef17e6ffbd5fcc3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1392,22 +1384,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://career.luxoft.com/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Regular Software Engineer Java Krakow Poland</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
+          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1417,17 +1409,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer java</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1437,19 +1429,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>db41fec42eff7fc7</t>
+          <t>958584b0e00fb2a6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1479,7 +1471,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1526,7 +1518,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7e7876fb53aec018</t>
+          <t>e0c2e763389249fb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1556,7 +1548,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1603,7 +1595,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>c7d16ed243960564</t>
+          <t>f59eedfdb81604eb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1633,7 +1625,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1680,7 +1672,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06c47b6859dcf9d9</t>
+          <t>6639b28e3e83df1b</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1710,7 +1702,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1757,7 +1749,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3add5db664f895b3</t>
+          <t>db41fec42eff7fc7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1787,7 +1779,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1834,7 +1826,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>75512c01a06f9149</t>
+          <t>7e7876fb53aec018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1864,7 +1856,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1911,7 +1903,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>e6f90d90e6d9ac49</t>
+          <t>c7d16ed243960564</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1941,7 +1933,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1988,7 +1980,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bcf6618b2c949330</t>
+          <t>06c47b6859dcf9d9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2018,7 +2010,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2065,7 +2057,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00340054a5ab077b</t>
+          <t>3add5db664f895b3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2095,7 +2087,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2142,7 +2134,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>521187917c773da4</t>
+          <t>75512c01a06f9149</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2172,7 +2164,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2219,7 +2211,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>39d7af8a3712173d</t>
+          <t>e6f90d90e6d9ac49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2249,7 +2241,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2296,7 +2288,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>b35b4abb2ec1b6cf</t>
+          <t>bcf6618b2c949330</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2326,7 +2318,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2373,7 +2365,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cc643671602a4ad6</t>
+          <t>00340054a5ab077b</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2403,7 +2395,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2450,7 +2442,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>e89acee1e60e4e15</t>
+          <t>521187917c773da4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2480,7 +2472,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2527,7 +2519,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>e2c7cfa23e04ecc5</t>
+          <t>39d7af8a3712173d</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2557,7 +2549,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2604,7 +2596,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>f264b25e9b13643e</t>
+          <t>b35b4abb2ec1b6cf</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2634,7 +2626,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2681,12 +2673,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>d4301ec4cb541a49</t>
+          <t>cc643671602a4ad6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2711,7 +2703,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-java-angular-and-cloud-services-publics-bordeaux-in-merignac-france-jid-216</t>
+          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2721,7 +2713,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2731,12 +2723,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2746,24 +2738,24 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5a9a92ff42d402b5</t>
+          <t>e89acee1e60e4e15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2788,7 +2780,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-full-stack-monetique-typescript-go-services-financiers-paris-kanest-xgen-in-courbevoie-france-jid-9847</t>
+          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2798,7 +2790,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2808,12 +2800,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2823,24 +2815,24 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>f10b2d50a2eab2ed</t>
+          <t>e2c7cfa23e04ecc5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2865,7 +2857,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-de-solutions-de-test-monetique-services-financiers-paris-kanest-in-courbevoie-france-jid-9846</t>
+          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2875,7 +2867,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2885,12 +2877,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2900,24 +2892,24 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>d37352caded60682</t>
+          <t>f264b25e9b13643e</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2942,7 +2934,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/reconversion-consultant-e-sap-toulouse-in-colomiers-france-jid-9845</t>
+          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2952,7 +2944,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2962,12 +2954,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2977,19 +2969,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ac20d4a800fe2783</t>
+          <t>d4301ec4cb541a49</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3019,7 +3011,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/devops-test-engineer-in-nieuwegein-netherlands-jid-4314</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-angular-and-cloud-services-publics-bordeaux-in-merignac-france-jid-216</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3066,7 +3058,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dfa7136b5b89a9fe</t>
+          <t>5a9a92ff42d402b5</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3096,7 +3088,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/qa-consultant-in-nieuwegein-netherlands-jid-5365</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-full-stack-monetique-typescript-go-services-financiers-paris-kanest-xgen-in-courbevoie-france-jid-9847</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3143,7 +3135,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8c80575a53c5eeaa</t>
+          <t>f10b2d50a2eab2ed</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3173,7 +3165,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-python-devops-services-financiers-paris-in-paris-france-jid-8938</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-de-solutions-de-test-monetique-services-financiers-paris-kanest-in-courbevoie-france-jid-9846</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3220,7 +3212,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>c50aedde915c89b5</t>
+          <t>d37352caded60682</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3250,7 +3242,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-orleans-in-orleans-france-jid-7170</t>
+          <t>https://careers.soprasteria.com/job/reconversion-consultant-e-sap-toulouse-in-colomiers-france-jid-9845</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3297,7 +3289,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06c5acd32fb73502</t>
+          <t>ac20d4a800fe2783</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3327,7 +3319,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-react-angular-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7171</t>
+          <t>https://careers.soprasteria.com/job/devops-test-engineer-in-nieuwegein-netherlands-jid-4314</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3374,7 +3366,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7947819c85cba4b7</t>
+          <t>dfa7136b5b89a9fe</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3404,7 +3396,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4782</t>
+          <t>https://careers.soprasteria.com/job/qa-consultant-in-nieuwegein-netherlands-jid-5365</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3451,7 +3443,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ee86d75ecad18f62</t>
+          <t>8c80575a53c5eeaa</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3481,7 +3473,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-expert-java-services-financiers-ile-de-france-in-paris-france-jid-4806</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-python-devops-services-financiers-paris-in-paris-france-jid-8938</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3528,7 +3520,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>138c41eaeddd3365</t>
+          <t>c50aedde915c89b5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3558,7 +3550,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/ingenieur-e-systemes-calculateurs-embarques-industrie-le-plessis-robinson-in-le-plessis-robinson-france-jid-9463</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-orleans-in-orleans-france-jid-7170</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3605,7 +3597,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>83618a239b34fb89</t>
+          <t>06c5acd32fb73502</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3635,7 +3627,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-java-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7169</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-react-angular-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7171</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3682,7 +3674,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6edaac1727441aa5</t>
+          <t>7947819c85cba4b7</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3712,7 +3704,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4790</t>
+          <t>https://careers.soprasteria.com/job/developpeur-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4782</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3759,7 +3751,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6c16f2ba70ae52ae</t>
+          <t>ee86d75ecad18f62</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3789,7 +3781,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/junior-support-engineer-24-7-in-brussels-belgium-jid-1614</t>
+          <t>https://careers.soprasteria.com/job/developpeur-expert-java-services-financiers-ile-de-france-in-paris-france-jid-4806</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3836,7 +3828,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>50bdd6d8ed2ce309</t>
+          <t>138c41eaeddd3365</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3866,7 +3858,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/test-automation-consultant-in-nieuwegein-netherlands-jid-4313</t>
+          <t>https://careers.soprasteria.com/job/ingenieur-e-systemes-calculateurs-embarques-industrie-le-plessis-robinson-in-le-plessis-robinson-france-jid-9463</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3913,7 +3905,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>27c9ec0a346e8d8a</t>
+          <t>83618a239b34fb89</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3943,7 +3935,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/chef-de-projet-it-adjoint-defense-and-securite-rennes-in-cesson-sevigne-france-jid-3750</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7169</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3990,7 +3982,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>12e5e7e963276a4f</t>
+          <t>6edaac1727441aa5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4020,7 +4012,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/bps-non-voice-team-member-six-month-contractual-job-in-chennai-tamil-nadu-india-jid-9844</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4790</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4067,7 +4059,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>9d6a28477b4aeb27</t>
+          <t>6c16f2ba70ae52ae</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4097,7 +4089,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/cybersecurity-team-lead-consultant-in-singapore-jid-9296</t>
+          <t>https://careers.soprasteria.com/job/junior-support-engineer-24-7-in-brussels-belgium-jid-1614</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4144,7 +4136,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>9f665ce19a03b2ab</t>
+          <t>50bdd6d8ed2ce309</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4174,7 +4166,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/manager-anti-financial-crime-operations-ai-and-managed-services-m-w-d-in-bundesweit-germany-jid-9843</t>
+          <t>https://careers.soprasteria.com/job/test-automation-consultant-in-nieuwegein-netherlands-jid-4313</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4221,7 +4213,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2718ac706b7b8fca</t>
+          <t>27c9ec0a346e8d8a</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4246,12 +4238,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shortlisted</t>
+          <t>Read more</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/#/</t>
+          <t>https://careers.soprasteria.com/job/chef-de-projet-it-adjoint-defense-and-securite-rennes-in-cesson-sevigne-france-jid-3750</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4286,7 +4278,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4298,82 +4290,390 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>12e5e7e963276a4f</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/bps-non-voice-team-member-six-month-contractual-job-in-chennai-tamil-nadu-india-jid-9844</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>9d6a28477b4aeb27</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/cybersecurity-team-lead-consultant-in-singapore-jid-9296</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>9f665ce19a03b2ab</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/manager-anti-financial-crime-operations-ai-and-managed-services-m-w-d-in-bundesweit-germany-jid-9843</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2718ac706b7b8fca</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/#/</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>71596b406dea22d9</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>Sopra Steria</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Service-Based</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>https://www.soprasteria.com/careers</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>View all</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://careers.soprasteria.com/jobs</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>java</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>java/backend keyword</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>entry level</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Not Seen Today</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O51"/>
+  <autoFilter ref="A1:O55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -655,12 +655,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>100</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -807,12 +809,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>100</v>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -959,12 +963,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>100</v>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,12 +1117,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>100</v>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">

--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job History" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1141,12 +1141,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bad3b7db83f498d3</t>
+          <t>b19989b7af5945b5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1166,69 +1166,67 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Java Software Engineer with Japanese</t>
+          <t>Java Software Engineer (m/f/d)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://careers.dxc.com/job/23900875/java-software-engineer-with-japanese-tan-binh-vn/</t>
+          <t>https://careers.dxc.com/job/23847277/java-software-engineer-m-f-d-erfurt-de/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>software engineer</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>java</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>software engineer</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="L10" t="n">
+        <v>75</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f6e573ccef82cc55</t>
+          <t>bad3b7db83f498d3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>DXC Technology</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1238,32 +1236,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/</t>
+          <t>https://dxc.com/us/en/careers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Java Full Stack Remote United Kingdom United Kingdom of Great Britain and Northern Ireland</t>
+          <t>Java Software Engineer with Japanese</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26676</t>
+          <t>https://careers.dxc.com/job/23900875/java-software-engineer-with-japanese-tan-binh-vn/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>software engineer java</t>
+          <t>software engineer</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1273,7 +1271,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>65</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1283,19 +1281,19 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>e3814f0fe9843500</t>
+          <t>f6e573ccef82cc55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1320,12 +1318,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Java Full Stack Remote United States United States of America</t>
+          <t>Full Stack Software Engineer Java Full Stack Remote United Kingdom United Kingdom of Great Britain and Northern Ireland</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26677</t>
+          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26676</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1372,12 +1370,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>eef17e6ffbd5fcc3</t>
+          <t>e3814f0fe9843500</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1397,12 +1395,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Regular Software Engineer Java Krakow Poland</t>
+          <t>Full Stack Software Engineer Java Full Stack Remote United States United States of America</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
+          <t>https://career.luxoft.com/jobs/full-stack-software-engineer-26677</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1437,29 +1435,29 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>958584b0e00fb2a6</t>
+          <t>eef17e6ffbd5fcc3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1469,22 +1467,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://career.luxoft.com/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Regular Software Engineer Java Krakow Poland</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
+          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1494,17 +1492,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer java</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1514,19 +1512,19 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>e0c2e763389249fb</t>
+          <t>958584b0e00fb2a6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1556,7 +1554,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1603,7 +1601,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f59eedfdb81604eb</t>
+          <t>e0c2e763389249fb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1633,7 +1631,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1680,7 +1678,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6639b28e3e83df1b</t>
+          <t>f59eedfdb81604eb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1710,7 +1708,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1757,7 +1755,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>db41fec42eff7fc7</t>
+          <t>6639b28e3e83df1b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1787,7 +1785,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1834,7 +1832,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7e7876fb53aec018</t>
+          <t>db41fec42eff7fc7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1864,7 +1862,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1911,7 +1909,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>c7d16ed243960564</t>
+          <t>7e7876fb53aec018</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1941,7 +1939,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1988,7 +1986,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06c47b6859dcf9d9</t>
+          <t>c7d16ed243960564</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2018,7 +2016,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2065,7 +2063,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3add5db664f895b3</t>
+          <t>06c47b6859dcf9d9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2095,7 +2093,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2142,7 +2140,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>75512c01a06f9149</t>
+          <t>3add5db664f895b3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2172,7 +2170,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2219,7 +2217,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>e6f90d90e6d9ac49</t>
+          <t>75512c01a06f9149</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2249,7 +2247,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2296,7 +2294,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bcf6618b2c949330</t>
+          <t>e6f90d90e6d9ac49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2326,7 +2324,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2373,7 +2371,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00340054a5ab077b</t>
+          <t>bcf6618b2c949330</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2403,7 +2401,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2450,7 +2448,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>521187917c773da4</t>
+          <t>00340054a5ab077b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2480,7 +2478,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2527,7 +2525,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>39d7af8a3712173d</t>
+          <t>521187917c773da4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2557,7 +2555,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2604,7 +2602,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>b35b4abb2ec1b6cf</t>
+          <t>39d7af8a3712173d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2634,7 +2632,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2681,7 +2679,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cc643671602a4ad6</t>
+          <t>b35b4abb2ec1b6cf</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2711,7 +2709,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2758,7 +2756,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>e89acee1e60e4e15</t>
+          <t>cc643671602a4ad6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2788,7 +2786,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
+          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2835,7 +2833,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>e2c7cfa23e04ecc5</t>
+          <t>e89acee1e60e4e15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2865,7 +2863,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
+          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2912,7 +2910,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>f264b25e9b13643e</t>
+          <t>e2c7cfa23e04ecc5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2942,7 +2940,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
+          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2989,12 +2987,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>d4301ec4cb541a49</t>
+          <t>f264b25e9b13643e</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3019,7 +3017,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-java-angular-and-cloud-services-publics-bordeaux-in-merignac-france-jid-216</t>
+          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3029,7 +3027,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3039,12 +3037,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3054,19 +3052,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5a9a92ff42d402b5</t>
+          <t>d4301ec4cb541a49</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3096,7 +3094,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-full-stack-monetique-typescript-go-services-financiers-paris-kanest-xgen-in-courbevoie-france-jid-9847</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-angular-and-cloud-services-publics-bordeaux-in-merignac-france-jid-216</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3143,7 +3141,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>f10b2d50a2eab2ed</t>
+          <t>5a9a92ff42d402b5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3173,7 +3171,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-de-solutions-de-test-monetique-services-financiers-paris-kanest-in-courbevoie-france-jid-9846</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-full-stack-monetique-typescript-go-services-financiers-paris-kanest-xgen-in-courbevoie-france-jid-9847</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3220,7 +3218,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>d37352caded60682</t>
+          <t>f10b2d50a2eab2ed</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3250,7 +3248,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/reconversion-consultant-e-sap-toulouse-in-colomiers-france-jid-9845</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-de-solutions-de-test-monetique-services-financiers-paris-kanest-in-courbevoie-france-jid-9846</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3297,7 +3295,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ac20d4a800fe2783</t>
+          <t>d37352caded60682</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3327,7 +3325,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/devops-test-engineer-in-nieuwegein-netherlands-jid-4314</t>
+          <t>https://careers.soprasteria.com/job/reconversion-consultant-e-sap-toulouse-in-colomiers-france-jid-9845</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3374,7 +3372,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dfa7136b5b89a9fe</t>
+          <t>ac20d4a800fe2783</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3404,7 +3402,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/qa-consultant-in-nieuwegein-netherlands-jid-5365</t>
+          <t>https://careers.soprasteria.com/job/devops-test-engineer-in-nieuwegein-netherlands-jid-4314</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3451,7 +3449,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8c80575a53c5eeaa</t>
+          <t>dfa7136b5b89a9fe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3481,7 +3479,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-python-devops-services-financiers-paris-in-paris-france-jid-8938</t>
+          <t>https://careers.soprasteria.com/job/qa-consultant-in-nieuwegein-netherlands-jid-5365</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3528,7 +3526,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>c50aedde915c89b5</t>
+          <t>8c80575a53c5eeaa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3558,7 +3556,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-orleans-in-orleans-france-jid-7170</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-python-devops-services-financiers-paris-in-paris-france-jid-8938</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3605,7 +3603,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06c5acd32fb73502</t>
+          <t>c50aedde915c89b5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3635,7 +3633,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-react-angular-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7171</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-orleans-in-orleans-france-jid-7170</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3682,7 +3680,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7947819c85cba4b7</t>
+          <t>06c5acd32fb73502</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3712,7 +3710,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4782</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-react-angular-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7171</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3759,7 +3757,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ee86d75ecad18f62</t>
+          <t>7947819c85cba4b7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3789,7 +3787,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-expert-java-services-financiers-ile-de-france-in-paris-france-jid-4806</t>
+          <t>https://careers.soprasteria.com/job/developpeur-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4782</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3836,7 +3834,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>138c41eaeddd3365</t>
+          <t>ee86d75ecad18f62</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3866,7 +3864,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/ingenieur-e-systemes-calculateurs-embarques-industrie-le-plessis-robinson-in-le-plessis-robinson-france-jid-9463</t>
+          <t>https://careers.soprasteria.com/job/developpeur-expert-java-services-financiers-ile-de-france-in-paris-france-jid-4806</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3913,7 +3911,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>83618a239b34fb89</t>
+          <t>138c41eaeddd3365</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3943,7 +3941,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-java-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7169</t>
+          <t>https://careers.soprasteria.com/job/ingenieur-e-systemes-calculateurs-embarques-industrie-le-plessis-robinson-in-le-plessis-robinson-france-jid-9463</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3990,7 +3988,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6edaac1727441aa5</t>
+          <t>83618a239b34fb89</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4020,7 +4018,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4790</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7169</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4067,7 +4065,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6c16f2ba70ae52ae</t>
+          <t>6edaac1727441aa5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4097,7 +4095,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/junior-support-engineer-24-7-in-brussels-belgium-jid-1614</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4790</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4144,7 +4142,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>50bdd6d8ed2ce309</t>
+          <t>6c16f2ba70ae52ae</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4174,7 +4172,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/test-automation-consultant-in-nieuwegein-netherlands-jid-4313</t>
+          <t>https://careers.soprasteria.com/job/junior-support-engineer-24-7-in-brussels-belgium-jid-1614</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4221,7 +4219,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>27c9ec0a346e8d8a</t>
+          <t>50bdd6d8ed2ce309</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4251,7 +4249,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/chef-de-projet-it-adjoint-defense-and-securite-rennes-in-cesson-sevigne-france-jid-3750</t>
+          <t>https://careers.soprasteria.com/job/test-automation-consultant-in-nieuwegein-netherlands-jid-4313</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4298,7 +4296,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12e5e7e963276a4f</t>
+          <t>27c9ec0a346e8d8a</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4328,7 +4326,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/bps-non-voice-team-member-six-month-contractual-job-in-chennai-tamil-nadu-india-jid-9844</t>
+          <t>https://careers.soprasteria.com/job/chef-de-projet-it-adjoint-defense-and-securite-rennes-in-cesson-sevigne-france-jid-3750</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4375,7 +4373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9d6a28477b4aeb27</t>
+          <t>12e5e7e963276a4f</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4405,7 +4403,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/cybersecurity-team-lead-consultant-in-singapore-jid-9296</t>
+          <t>https://careers.soprasteria.com/job/bps-non-voice-team-member-six-month-contractual-job-in-chennai-tamil-nadu-india-jid-9844</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4452,7 +4450,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9f665ce19a03b2ab</t>
+          <t>9d6a28477b4aeb27</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4482,7 +4480,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/manager-anti-financial-crime-operations-ai-and-managed-services-m-w-d-in-bundesweit-germany-jid-9843</t>
+          <t>https://careers.soprasteria.com/job/cybersecurity-team-lead-consultant-in-singapore-jid-9296</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4529,7 +4527,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2718ac706b7b8fca</t>
+          <t>9f665ce19a03b2ab</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4554,12 +4552,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shortlisted</t>
+          <t>Read more</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/#/</t>
+          <t>https://careers.soprasteria.com/job/manager-anti-financial-crime-operations-ai-and-managed-services-m-w-d-in-bundesweit-germany-jid-9843</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4594,7 +4592,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4606,82 +4604,159 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>2718ac706b7b8fca</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/#/</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>71596b406dea22d9</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>Sopra Steria</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Service-Based</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>https://www.soprasteria.com/careers</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>View all</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://careers.soprasteria.com/jobs</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>java</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>java/backend keyword</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>entry level</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Not Seen Today</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O55"/>
+  <autoFilter ref="A1:O56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -1194,8 +1194,10 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>75</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>

--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -1201,7 +1201,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">

--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job History" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1449,12 +1449,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>eef17e6ffbd5fcc3</t>
+          <t>bf71e91ea86310f1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1474,27 +1474,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Regular Software Engineer Java Krakow Poland</t>
+          <t>Regular Java Backend Software Engineer Bucharest, Romania Java</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
+          <t>https://career.luxoft.com/jobs/regular-java-backend-software-engineer-28342</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bengaluru, India, Hyderabad, Noida, Gurugram</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>software engineer java</t>
+          <t>software engineer</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1502,41 +1502,39 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="L14" t="n">
+        <v>75</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>958584b0e00fb2a6</t>
+          <t>eef17e6ffbd5fcc3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1546,22 +1544,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://career.luxoft.com/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Regular Software Engineer Java Krakow Poland</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
+          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1571,17 +1569,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer java</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1591,19 +1589,19 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>e0c2e763389249fb</t>
+          <t>958584b0e00fb2a6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1633,7 +1631,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1680,7 +1678,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>f59eedfdb81604eb</t>
+          <t>e0c2e763389249fb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1710,7 +1708,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1757,7 +1755,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6639b28e3e83df1b</t>
+          <t>f59eedfdb81604eb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1787,7 +1785,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1834,7 +1832,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>db41fec42eff7fc7</t>
+          <t>6639b28e3e83df1b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1864,7 +1862,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1911,7 +1909,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7e7876fb53aec018</t>
+          <t>db41fec42eff7fc7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1941,7 +1939,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1988,7 +1986,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>c7d16ed243960564</t>
+          <t>7e7876fb53aec018</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2018,7 +2016,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2065,7 +2063,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06c47b6859dcf9d9</t>
+          <t>c7d16ed243960564</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2095,7 +2093,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2142,7 +2140,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3add5db664f895b3</t>
+          <t>06c47b6859dcf9d9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2172,7 +2170,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2219,7 +2217,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>75512c01a06f9149</t>
+          <t>3add5db664f895b3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2249,7 +2247,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2296,7 +2294,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>e6f90d90e6d9ac49</t>
+          <t>75512c01a06f9149</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2326,7 +2324,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2373,7 +2371,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bcf6618b2c949330</t>
+          <t>e6f90d90e6d9ac49</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2403,7 +2401,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2450,7 +2448,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00340054a5ab077b</t>
+          <t>bcf6618b2c949330</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2480,7 +2478,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2527,7 +2525,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>521187917c773da4</t>
+          <t>00340054a5ab077b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2557,7 +2555,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2604,7 +2602,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>39d7af8a3712173d</t>
+          <t>521187917c773da4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2634,7 +2632,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2681,7 +2679,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>b35b4abb2ec1b6cf</t>
+          <t>39d7af8a3712173d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2711,7 +2709,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2758,7 +2756,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cc643671602a4ad6</t>
+          <t>b35b4abb2ec1b6cf</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2788,7 +2786,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2835,7 +2833,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>e89acee1e60e4e15</t>
+          <t>cc643671602a4ad6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2865,7 +2863,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
+          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2912,7 +2910,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>e2c7cfa23e04ecc5</t>
+          <t>e89acee1e60e4e15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2942,7 +2940,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
+          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2989,7 +2987,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>f264b25e9b13643e</t>
+          <t>e2c7cfa23e04ecc5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3019,7 +3017,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
+          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3066,12 +3064,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>d4301ec4cb541a49</t>
+          <t>f264b25e9b13643e</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3096,7 +3094,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-java-angular-and-cloud-services-publics-bordeaux-in-merignac-france-jid-216</t>
+          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3106,7 +3104,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3116,12 +3114,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3131,19 +3129,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5a9a92ff42d402b5</t>
+          <t>d4301ec4cb541a49</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3173,7 +3171,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-full-stack-monetique-typescript-go-services-financiers-paris-kanest-xgen-in-courbevoie-france-jid-9847</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-angular-and-cloud-services-publics-bordeaux-in-merignac-france-jid-216</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3220,7 +3218,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>f10b2d50a2eab2ed</t>
+          <t>5a9a92ff42d402b5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3250,7 +3248,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-de-solutions-de-test-monetique-services-financiers-paris-kanest-in-courbevoie-france-jid-9846</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-full-stack-monetique-typescript-go-services-financiers-paris-kanest-xgen-in-courbevoie-france-jid-9847</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3297,7 +3295,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>d37352caded60682</t>
+          <t>f10b2d50a2eab2ed</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3327,7 +3325,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/reconversion-consultant-e-sap-toulouse-in-colomiers-france-jid-9845</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-de-solutions-de-test-monetique-services-financiers-paris-kanest-in-courbevoie-france-jid-9846</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3374,7 +3372,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ac20d4a800fe2783</t>
+          <t>d37352caded60682</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3404,7 +3402,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/devops-test-engineer-in-nieuwegein-netherlands-jid-4314</t>
+          <t>https://careers.soprasteria.com/job/reconversion-consultant-e-sap-toulouse-in-colomiers-france-jid-9845</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3451,7 +3449,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dfa7136b5b89a9fe</t>
+          <t>ac20d4a800fe2783</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3481,7 +3479,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/qa-consultant-in-nieuwegein-netherlands-jid-5365</t>
+          <t>https://careers.soprasteria.com/job/devops-test-engineer-in-nieuwegein-netherlands-jid-4314</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3528,7 +3526,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8c80575a53c5eeaa</t>
+          <t>dfa7136b5b89a9fe</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3558,7 +3556,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-python-devops-services-financiers-paris-in-paris-france-jid-8938</t>
+          <t>https://careers.soprasteria.com/job/qa-consultant-in-nieuwegein-netherlands-jid-5365</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3605,7 +3603,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>c50aedde915c89b5</t>
+          <t>8c80575a53c5eeaa</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3635,7 +3633,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-orleans-in-orleans-france-jid-7170</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-python-devops-services-financiers-paris-in-paris-france-jid-8938</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3682,7 +3680,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06c5acd32fb73502</t>
+          <t>c50aedde915c89b5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3712,7 +3710,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-react-angular-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7171</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-orleans-in-orleans-france-jid-7170</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3759,7 +3757,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7947819c85cba4b7</t>
+          <t>06c5acd32fb73502</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3789,7 +3787,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4782</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-react-angular-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7171</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3836,7 +3834,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ee86d75ecad18f62</t>
+          <t>7947819c85cba4b7</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3866,7 +3864,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-expert-java-services-financiers-ile-de-france-in-paris-france-jid-4806</t>
+          <t>https://careers.soprasteria.com/job/developpeur-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4782</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3913,7 +3911,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>138c41eaeddd3365</t>
+          <t>ee86d75ecad18f62</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3943,7 +3941,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/ingenieur-e-systemes-calculateurs-embarques-industrie-le-plessis-robinson-in-le-plessis-robinson-france-jid-9463</t>
+          <t>https://careers.soprasteria.com/job/developpeur-expert-java-services-financiers-ile-de-france-in-paris-france-jid-4806</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3990,7 +3988,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>83618a239b34fb89</t>
+          <t>138c41eaeddd3365</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4020,7 +4018,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-java-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7169</t>
+          <t>https://careers.soprasteria.com/job/ingenieur-e-systemes-calculateurs-embarques-industrie-le-plessis-robinson-in-le-plessis-robinson-france-jid-9463</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4067,7 +4065,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6edaac1727441aa5</t>
+          <t>83618a239b34fb89</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4097,7 +4095,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4790</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7169</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4144,7 +4142,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6c16f2ba70ae52ae</t>
+          <t>6edaac1727441aa5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4174,7 +4172,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/junior-support-engineer-24-7-in-brussels-belgium-jid-1614</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4790</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4221,7 +4219,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>50bdd6d8ed2ce309</t>
+          <t>6c16f2ba70ae52ae</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4251,7 +4249,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/test-automation-consultant-in-nieuwegein-netherlands-jid-4313</t>
+          <t>https://careers.soprasteria.com/job/junior-support-engineer-24-7-in-brussels-belgium-jid-1614</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4298,7 +4296,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>27c9ec0a346e8d8a</t>
+          <t>50bdd6d8ed2ce309</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4328,7 +4326,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/chef-de-projet-it-adjoint-defense-and-securite-rennes-in-cesson-sevigne-france-jid-3750</t>
+          <t>https://careers.soprasteria.com/job/test-automation-consultant-in-nieuwegein-netherlands-jid-4313</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4375,7 +4373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12e5e7e963276a4f</t>
+          <t>27c9ec0a346e8d8a</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4405,7 +4403,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/bps-non-voice-team-member-six-month-contractual-job-in-chennai-tamil-nadu-india-jid-9844</t>
+          <t>https://careers.soprasteria.com/job/chef-de-projet-it-adjoint-defense-and-securite-rennes-in-cesson-sevigne-france-jid-3750</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4452,7 +4450,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9d6a28477b4aeb27</t>
+          <t>12e5e7e963276a4f</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4482,7 +4480,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/cybersecurity-team-lead-consultant-in-singapore-jid-9296</t>
+          <t>https://careers.soprasteria.com/job/bps-non-voice-team-member-six-month-contractual-job-in-chennai-tamil-nadu-india-jid-9844</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4529,7 +4527,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9f665ce19a03b2ab</t>
+          <t>9d6a28477b4aeb27</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4559,7 +4557,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/manager-anti-financial-crime-operations-ai-and-managed-services-m-w-d-in-bundesweit-germany-jid-9843</t>
+          <t>https://careers.soprasteria.com/job/cybersecurity-team-lead-consultant-in-singapore-jid-9296</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4606,7 +4604,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2718ac706b7b8fca</t>
+          <t>9f665ce19a03b2ab</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4631,12 +4629,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Shortlisted</t>
+          <t>Read more</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/#/</t>
+          <t>https://careers.soprasteria.com/job/manager-anti-financial-crime-operations-ai-and-managed-services-m-w-d-in-bundesweit-germany-jid-9843</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4671,7 +4669,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4683,82 +4681,159 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>2718ac706b7b8fca</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/#/</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>71596b406dea22d9</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>Sopra Steria</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Service-Based</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>https://www.soprasteria.com/careers</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>View all</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>https://careers.soprasteria.com/jobs</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>java</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>java/backend keyword</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>entry level</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Not Seen Today</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O56"/>
+  <autoFilter ref="A1:O57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -1502,12 +1502,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>75</v>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">

--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Job History" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job History'!$A$1:$O$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1449,12 +1449,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bf71e91ea86310f1</t>
+          <t>4e694fb70858753b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1474,17 +1474,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Regular Java Backend Software Engineer Bucharest, Romania Java</t>
+          <t>Java Developer (Sun - Thu) Remote India, India Java Full Stack</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/regular-java-backend-software-engineer-28342</t>
+          <t>https://career.luxoft.com/jobs/java-developer-sun-thu-28498</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bengaluru, India, Hyderabad, Noida, Gurugram</t>
+          <t>India, Remote, Hyderabad</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>software engineer</t>
+          <t>java developer</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1502,36 +1502,34 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="L14" t="n">
+        <v>100</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>eef17e6ffbd5fcc3</t>
+          <t>6059bba6e97c2f8c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1551,27 +1549,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Regular Software Engineer Java Krakow Poland</t>
+          <t>Java Developer (Tue - Sat) Remote India, India Java Full Stack</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
+          <t>https://career.luxoft.com/jobs/java-developer-tue-sat-28499</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>India, Remote, Hyderabad</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>software engineer java</t>
+          <t>java developer</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1579,41 +1577,39 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="L15" t="n">
+        <v>100</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Not Seen Today</t>
+          <t>New</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>958584b0e00fb2a6</t>
+          <t>bf71e91ea86310f1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1623,42 +1619,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://career.luxoft.com/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Regular Java Backend Software Engineer Bucharest, Romania Java</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
+          <t>https://career.luxoft.com/jobs/regular-java-backend-software-engineer-28342</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Bengaluru, India, Hyderabad, Noida, Gurugram</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>java, git</t>
+          <t>java</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>75</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1668,29 +1664,29 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>e0c2e763389249fb</t>
+          <t>eef17e6ffbd5fcc3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1700,22 +1696,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.soprasteria.com/careers</t>
+          <t>https://career.luxoft.com/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Read more</t>
+          <t>Regular Software Engineer Java Krakow Poland</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
+          <t>https://career.luxoft.com/jobs/regular-software-engineer-26719</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>India</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1725,17 +1721,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>java/backend keyword</t>
+          <t>software engineer java</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>associate</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>103</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1745,19 +1741,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f59eedfdb81604eb</t>
+          <t>958584b0e00fb2a6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1787,7 +1783,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-euse-java-aix-en-provence-in-aix-en-provence-france-jid-5854</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1834,7 +1830,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6639b28e3e83df1b</t>
+          <t>e0c2e763389249fb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1864,7 +1860,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-transport-and-mobility-m-w-d-in-bundesweit-germany-jid-7385</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1911,7 +1907,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>db41fec42eff7fc7</t>
+          <t>f59eedfdb81604eb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1941,7 +1937,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sales-and-growth-im-produktgeschaeft-m-w-d-in-hamburg-germany-jid-9258</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1988,7 +1984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7e7876fb53aec018</t>
+          <t>6639b28e3e83df1b</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2018,7 +2014,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-sap-data-and-analytics-m-w-d-in-bundesweit-germany-jid-2750</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2065,7 +2061,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>c7d16ed243960564</t>
+          <t>db41fec42eff7fc7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2095,7 +2091,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-project-management-office-im-public-sector-m-w-d-in-bundesweit-germany-jid-2906</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2142,7 +2138,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06c47b6859dcf9d9</t>
+          <t>7e7876fb53aec018</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2172,7 +2168,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-mit-schwerpunkt-fachliche-unterstuetzung-in-leitstellenloesungen-m-w-d-in-berlin-frankfurt-germany-jid-9269</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2219,7 +2215,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3add5db664f895b3</t>
+          <t>c7d16ed243960564</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2249,7 +2245,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-java-entwicklung-m-w-d-in-leipzig-germany-jid-7640</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2296,7 +2292,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>75512c01a06f9149</t>
+          <t>06c47b6859dcf9d9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2326,7 +2322,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-integration-and-service-schwerpunkt-it-m-w-d-in-berlin-frankfurt-germany-jid-9270</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2373,7 +2369,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>e6f90d90e6d9ac49</t>
+          <t>3add5db664f895b3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2403,7 +2399,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-frontend-and-backend-entwicklung-m-w-d-in-hamburg-germany-jid-2655</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2450,7 +2446,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bcf6618b2c949330</t>
+          <t>75512c01a06f9149</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2480,7 +2476,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-entwickler-prozessautomatisierung-m-w-d-in-bundesweit-germany-jid-9511</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2527,7 +2523,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00340054a5ab077b</t>
+          <t>e6f90d90e6d9ac49</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2557,7 +2553,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-data-engineer-analyst-m-w-d-in-hamburg-germany-jid-3431</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2604,7 +2600,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>521187917c773da4</t>
+          <t>bcf6618b2c949330</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2634,7 +2630,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-devsecops-im-solution-center-m-w-d-in-berlin-frankfurt-germany-jid-9280</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2681,7 +2677,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>39d7af8a3712173d</t>
+          <t>00340054a5ab077b</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2711,7 +2707,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cybersecurity-m-w-d-in-bundesweit-germany-jid-3153</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2758,7 +2754,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>b35b4abb2ec1b6cf</t>
+          <t>521187917c773da4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2788,7 +2784,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-cyber-security-vulnerability-management-and-edr-m-w-d-in-muenchen-germany-jid-9255</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2835,7 +2831,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cc643671602a4ad6</t>
+          <t>39d7af8a3712173d</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2865,7 +2861,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-accounting-and-finanzprozesse-m-w-d-purchase-to-pay-p2p-in-bundesweit-germany-jid-9250</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2912,7 +2908,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>e89acee1e60e4e15</t>
+          <t>b35b4abb2ec1b6cf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2942,7 +2938,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
+          <t>https://careers.soprasteria.com/job/werkstudent-m-w-d-hr-digitalisierung-and-prozessautomatisierung-am-standort-hamburg-in-hamburg-germany-jid-9329</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2989,7 +2985,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>e2c7cfa23e04ecc5</t>
+          <t>cc643671602a4ad6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3019,7 +3015,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
+          <t>https://careers.soprasteria.com/job/vil-du-v-re-med-a-forme-lede-fremtidens-utviklermilj-pa-hamar-in-hamar-norway-jid-9560</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3066,7 +3062,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>f264b25e9b13643e</t>
+          <t>e89acee1e60e4e15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3096,7 +3092,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
+          <t>https://careers.soprasteria.com/job/business-owner-erp-in-stockholm-sweden-jid-9545</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3143,12 +3139,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>d4301ec4cb541a49</t>
+          <t>e2c7cfa23e04ecc5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3173,7 +3169,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-java-angular-and-cloud-services-publics-bordeaux-in-merignac-france-jid-216</t>
+          <t>https://careers.soprasteria.com/job/ingeniero-cloud-in-madrid-spain-jid-9559</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3183,7 +3179,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3193,12 +3189,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3208,24 +3204,24 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5a9a92ff42d402b5</t>
+          <t>f264b25e9b13643e</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3250,7 +3246,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-full-stack-monetique-typescript-go-services-financiers-paris-kanest-xgen-in-courbevoie-france-jid-9847</t>
+          <t>https://careers.soprasteria.com/job/manager-adjoint-e-strategie-cybersecurite-toulouse-in-toulouse-france-jid-7122</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3260,7 +3256,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>java</t>
+          <t>java, git</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3270,12 +3266,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3285,19 +3281,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>f10b2d50a2eab2ed</t>
+          <t>d4301ec4cb541a49</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3327,7 +3323,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/stage-developpeur-de-solutions-de-test-monetique-services-financiers-paris-kanest-in-courbevoie-france-jid-9846</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-angular-and-cloud-services-publics-bordeaux-in-merignac-france-jid-216</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3374,7 +3370,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>d37352caded60682</t>
+          <t>5a9a92ff42d402b5</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3404,7 +3400,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/reconversion-consultant-e-sap-toulouse-in-colomiers-france-jid-9845</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-full-stack-monetique-typescript-go-services-financiers-paris-kanest-xgen-in-courbevoie-france-jid-9847</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3451,7 +3447,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ac20d4a800fe2783</t>
+          <t>f10b2d50a2eab2ed</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3481,7 +3477,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/devops-test-engineer-in-nieuwegein-netherlands-jid-4314</t>
+          <t>https://careers.soprasteria.com/job/stage-developpeur-de-solutions-de-test-monetique-services-financiers-paris-kanest-in-courbevoie-france-jid-9846</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3528,7 +3524,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dfa7136b5b89a9fe</t>
+          <t>d37352caded60682</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3558,7 +3554,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/qa-consultant-in-nieuwegein-netherlands-jid-5365</t>
+          <t>https://careers.soprasteria.com/job/reconversion-consultant-e-sap-toulouse-in-colomiers-france-jid-9845</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3605,7 +3601,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8c80575a53c5eeaa</t>
+          <t>ac20d4a800fe2783</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3635,7 +3631,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-python-devops-services-financiers-paris-in-paris-france-jid-8938</t>
+          <t>https://careers.soprasteria.com/job/devops-test-engineer-in-nieuwegein-netherlands-jid-4314</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3682,7 +3678,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>c50aedde915c89b5</t>
+          <t>dfa7136b5b89a9fe</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3712,7 +3708,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-orleans-in-orleans-france-jid-7170</t>
+          <t>https://careers.soprasteria.com/job/qa-consultant-in-nieuwegein-netherlands-jid-5365</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3759,7 +3755,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06c5acd32fb73502</t>
+          <t>8c80575a53c5eeaa</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3789,7 +3785,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-react-angular-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7171</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-python-devops-services-financiers-paris-in-paris-france-jid-8938</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3836,7 +3832,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>7947819c85cba4b7</t>
+          <t>c50aedde915c89b5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3866,7 +3862,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4782</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-orleans-in-orleans-france-jid-7170</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3913,7 +3909,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ee86d75ecad18f62</t>
+          <t>06c5acd32fb73502</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3943,7 +3939,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-expert-java-services-financiers-ile-de-france-in-paris-france-jid-4806</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-java-fullstack-react-angular-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7171</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3990,7 +3986,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>138c41eaeddd3365</t>
+          <t>7947819c85cba4b7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4020,7 +4016,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/ingenieur-e-systemes-calculateurs-embarques-industrie-le-plessis-robinson-in-le-plessis-robinson-france-jid-9463</t>
+          <t>https://careers.soprasteria.com/job/developpeur-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4782</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4067,7 +4063,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>83618a239b34fb89</t>
+          <t>ee86d75ecad18f62</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4097,7 +4093,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/developpeur-se-java-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7169</t>
+          <t>https://careers.soprasteria.com/job/developpeur-expert-java-services-financiers-ile-de-france-in-paris-france-jid-4806</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4144,7 +4140,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6edaac1727441aa5</t>
+          <t>138c41eaeddd3365</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4174,7 +4170,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/tech-lead-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4790</t>
+          <t>https://careers.soprasteria.com/job/ingenieur-e-systemes-calculateurs-embarques-industrie-le-plessis-robinson-in-le-plessis-robinson-france-jid-9463</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4221,7 +4217,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6c16f2ba70ae52ae</t>
+          <t>83618a239b34fb89</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4251,7 +4247,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/junior-support-engineer-24-7-in-brussels-belgium-jid-1614</t>
+          <t>https://careers.soprasteria.com/job/developpeur-se-java-services-financiers-lille-in-villeneuve-d-ascq-france-jid-7169</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4298,7 +4294,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>50bdd6d8ed2ce309</t>
+          <t>6edaac1727441aa5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4328,7 +4324,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/test-automation-consultant-in-nieuwegein-netherlands-jid-4313</t>
+          <t>https://careers.soprasteria.com/job/tech-lead-fullstack-java-react-services-financiers-ile-de-france-in-paris-france-jid-4790</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4375,7 +4371,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>27c9ec0a346e8d8a</t>
+          <t>6c16f2ba70ae52ae</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4405,7 +4401,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/chef-de-projet-it-adjoint-defense-and-securite-rennes-in-cesson-sevigne-france-jid-3750</t>
+          <t>https://careers.soprasteria.com/job/junior-support-engineer-24-7-in-brussels-belgium-jid-1614</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4452,7 +4448,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>12e5e7e963276a4f</t>
+          <t>50bdd6d8ed2ce309</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4482,7 +4478,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/bps-non-voice-team-member-six-month-contractual-job-in-chennai-tamil-nadu-india-jid-9844</t>
+          <t>https://careers.soprasteria.com/job/test-automation-consultant-in-nieuwegein-netherlands-jid-4313</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4529,7 +4525,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9d6a28477b4aeb27</t>
+          <t>27c9ec0a346e8d8a</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4559,7 +4555,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/cybersecurity-team-lead-consultant-in-singapore-jid-9296</t>
+          <t>https://careers.soprasteria.com/job/chef-de-projet-it-adjoint-defense-and-securite-rennes-in-cesson-sevigne-france-jid-3750</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4606,7 +4602,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9f665ce19a03b2ab</t>
+          <t>12e5e7e963276a4f</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4632,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/manager-anti-financial-crime-operations-ai-and-managed-services-m-w-d-in-bundesweit-germany-jid-9843</t>
+          <t>https://careers.soprasteria.com/job/bps-non-voice-team-member-six-month-contractual-job-in-chennai-tamil-nadu-india-jid-9844</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4683,7 +4679,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2718ac706b7b8fca</t>
+          <t>9d6a28477b4aeb27</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4708,12 +4704,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Shortlisted</t>
+          <t>Read more</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/#/</t>
+          <t>https://careers.soprasteria.com/job/cybersecurity-team-lead-consultant-in-singapore-jid-9296</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4748,7 +4744,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4760,82 +4756,236 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>9f665ce19a03b2ab</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Read more</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/job/manager-anti-financial-crime-operations-ai-and-managed-services-m-w-d-in-bundesweit-germany-jid-9843</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2718ac706b7b8fca</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Sopra Steria</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.soprasteria.com/careers</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Shortlisted</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://careers.soprasteria.com/#/</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>java</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>java/backend keyword</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>71596b406dea22d9</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>Sopra Steria</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Service-Based</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Service-Based</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>https://www.soprasteria.com/careers</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>View all</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://careers.soprasteria.com/jobs</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>java</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>java/backend keyword</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>entry level</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Not Seen Today</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Not Seen Today</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O57"/>
+  <autoFilter ref="A1:O59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/job_history.xlsx
+++ b/outputs/job_history.xlsx
@@ -1502,12 +1502,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>100</v>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1577,12 +1579,14 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>100</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Not Seen Today</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
